--- a/SFF2026-Program.xlsx
+++ b/SFF2026-Program.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bdemmler\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80BDDCB8-DE36-421C-B91B-C8E2696A5A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B8DB1EB-9516-4FA7-8746-D1A0E61B1D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="759" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Abstracts" sheetId="17" r:id="rId1"/>
+    <sheet name="Admin" sheetId="18" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3351" uniqueCount="1375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3353" uniqueCount="1377">
   <si>
     <t>Session Name</t>
   </si>
@@ -4161,6 +4162,12 @@
   </si>
   <si>
     <t>Real-Time Object Detection for Autonomous Robotic 3D Printing</t>
+  </si>
+  <si>
+    <t>07/01/2026</t>
+  </si>
+  <si>
+    <t>Revision Date</t>
   </si>
 </sst>
 </file>
@@ -4674,11 +4681,12 @@
     <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="18" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="20% - Accent1" xfId="18" builtinId="30" customBuiltin="1"/>
@@ -5019,7 +5027,7 @@
   <dimension ref="A1:Q305"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" customWidth="1"/>
+    <col min="1" max="1" width="89.7109375" customWidth="1"/>
     <col min="2" max="2" width="19.85546875" customWidth="1"/>
     <col min="3" max="3" width="18.42578125" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" customWidth="1"/>
@@ -21096,4 +21104,29 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D76266C9-E334-4D8E-A578-5780FE1FB26B}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B1" s="4"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>